--- a/Team-Data/2007-08/4-14-2007-08.xlsx
+++ b/Team-Data/2007-08/4-14-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>-1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
         <v>19</v>
@@ -754,7 +821,7 @@
         <v>4</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ2" t="n">
         <v>21</v>
@@ -790,7 +857,7 @@
         <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
         <v>24</v>
@@ -802,7 +869,7 @@
         <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
@@ -814,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.802</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -870,19 +937,19 @@
         <v>7.3</v>
       </c>
       <c r="M3" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O3" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="P3" t="n">
         <v>26.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R3" t="n">
         <v>10.1</v>
@@ -894,7 +961,7 @@
         <v>42</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V3" t="n">
         <v>15.2</v>
@@ -909,7 +976,7 @@
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA3" t="n">
         <v>22.2</v>
@@ -918,10 +985,10 @@
         <v>100.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -963,10 +1030,10 @@
         <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>13</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
         <v>4</v>
@@ -1130,7 +1197,7 @@
         <v>16</v>
       </c>
       <c r="AM4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN4" t="n">
         <v>12</v>
@@ -1172,10 +1239,10 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
         <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>0.395</v>
+        <v>0.388</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.435</v>
+        <v>0.431</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="O5" t="n">
         <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0.754</v>
       </c>
       <c r="R5" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S5" t="n">
         <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U5" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V5" t="n">
         <v>14.6</v>
@@ -1267,7 +1334,7 @@
         <v>7.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y5" t="n">
         <v>5.7</v>
@@ -1276,16 +1343,16 @@
         <v>21.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.2</v>
+        <v>96.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.2</v>
+        <v>-3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1297,10 +1364,10 @@
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1318,10 +1385,10 @@
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>17</v>
@@ -1333,19 +1400,19 @@
         <v>18</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>29</v>
@@ -1357,7 +1424,7 @@
         <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>0.556</v>
+        <v>0.55</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1407,13 +1474,13 @@
         <v>35.9</v>
       </c>
       <c r="J6" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M6" t="n">
         <v>19</v>
@@ -1425,16 +1492,16 @@
         <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.717</v>
+        <v>0.718</v>
       </c>
       <c r="R6" t="n">
         <v>13.3</v>
       </c>
       <c r="S6" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T6" t="n">
         <v>44.5</v>
@@ -1464,10 +1531,10 @@
         <v>96.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,16 +1546,16 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1527,7 +1594,7 @@
         <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -1536,10 +1603,10 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
         <v>16</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1697,7 +1764,7 @@
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
         <v>20</v>
@@ -1709,19 +1776,19 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1861,7 +1928,7 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2037,7 +2104,7 @@
         <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
         <v>22</v>
@@ -2049,7 +2116,7 @@
         <v>20</v>
       </c>
       <c r="AP9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ9" t="n">
         <v>14</v>
@@ -2061,7 +2128,7 @@
         <v>25</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>10</v>
@@ -2088,7 +2155,7 @@
         <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.593</v>
+        <v>0.6</v>
       </c>
       <c r="H10" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I10" t="n">
         <v>41.4</v>
       </c>
       <c r="J10" t="n">
-        <v>90.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.46</v>
@@ -2144,19 +2211,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O10" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R10" t="n">
         <v>12.6</v>
@@ -2168,10 +2235,10 @@
         <v>43.1</v>
       </c>
       <c r="U10" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V10" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W10" t="n">
         <v>9.1</v>
@@ -2180,37 +2247,37 @@
         <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB10" t="n">
         <v>110.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>12</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -2225,13 +2292,13 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -2243,7 +2310,7 @@
         <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
         <v>9</v>
@@ -2255,16 +2322,16 @@
         <v>2</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
         <v>54</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.667</v>
+        <v>0.675</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J11" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.449</v>
@@ -2332,70 +2399,70 @@
         <v>0.342</v>
       </c>
       <c r="O11" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P11" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.727</v>
+        <v>0.725</v>
       </c>
       <c r="R11" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S11" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T11" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
         <v>21.4</v>
       </c>
       <c r="V11" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W11" t="n">
         <v>7.3</v>
       </c>
       <c r="X11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y11" t="n">
         <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB11" t="n">
         <v>96.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK11" t="n">
         <v>19</v>
@@ -2410,16 +2477,16 @@
         <v>26</v>
       </c>
       <c r="AO11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP11" t="n">
         <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>6</v>
@@ -2428,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
@@ -2446,10 +2513,10 @@
         <v>6</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" t="n">
         <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2505,37 +2572,37 @@
         <v>0.443</v>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M12" t="n">
         <v>24.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
         <v>22.6</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W12" t="n">
         <v>7.6</v>
@@ -2550,7 +2617,7 @@
         <v>23.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB12" t="n">
         <v>103.6</v>
@@ -2559,7 +2626,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2580,7 +2647,7 @@
         <v>4</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2589,16 +2656,16 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2607,7 +2674,7 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2789,7 +2856,7 @@
         <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU13" t="n">
         <v>16</v>
@@ -2798,7 +2865,7 @@
         <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3126,7 +3193,7 @@
         <v>13</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
         <v>7</v>
@@ -3138,13 +3205,13 @@
         <v>21</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3153,7 +3220,7 @@
         <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>0.173</v>
+        <v>0.175</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="J16" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K16" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L16" t="n">
         <v>5.9</v>
       </c>
       <c r="M16" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N16" t="n">
         <v>0.357</v>
       </c>
       <c r="O16" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="R16" t="n">
         <v>9</v>
@@ -3275,19 +3342,19 @@
         <v>4.1</v>
       </c>
       <c r="Z16" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AA16" t="n">
         <v>20.3</v>
       </c>
-      <c r="AA16" t="n">
-        <v>20.2</v>
-      </c>
       <c r="AB16" t="n">
-        <v>91.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>-8.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
         <v>22</v>
@@ -3317,7 +3384,7 @@
         <v>21</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
@@ -3341,7 +3408,7 @@
         <v>25</v>
       </c>
       <c r="AV16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW16" t="n">
         <v>16</v>
@@ -3350,13 +3417,13 @@
         <v>23</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E17" t="n">
         <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>0.321</v>
+        <v>0.325</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J17" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
@@ -3421,13 +3488,13 @@
         <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O17" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q17" t="n">
         <v>0.733</v>
@@ -3439,10 +3506,10 @@
         <v>28.7</v>
       </c>
       <c r="T17" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U17" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V17" t="n">
         <v>14.7</v>
@@ -3454,22 +3521,22 @@
         <v>4.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB17" t="n">
-        <v>97</v>
+        <v>96.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.9</v>
+        <v>-6.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3484,13 +3551,13 @@
         <v>8</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
@@ -3517,13 +3584,13 @@
         <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
@@ -3538,10 +3605,10 @@
         <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BC17" t="n">
         <v>26</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3681,7 +3748,7 @@
         <v>25</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3699,13 +3766,13 @@
         <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -4054,7 +4121,7 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>14</v>
@@ -4066,13 +4133,13 @@
         <v>16</v>
       </c>
       <c r="AU20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21" t="n">
         <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4146,16 +4213,16 @@
         <v>5.9</v>
       </c>
       <c r="M21" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N21" t="n">
         <v>0.337</v>
       </c>
       <c r="O21" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P21" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0.725</v>
@@ -4164,10 +4231,10 @@
         <v>12.5</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U21" t="n">
         <v>18.6</v>
@@ -4191,40 +4258,40 @@
         <v>20.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC21" t="n">
         <v>-6.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
         <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ21" t="n">
         <v>10</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN21" t="n">
         <v>27</v>
@@ -4242,7 +4309,7 @@
         <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4254,7 +4321,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4266,10 +4333,10 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>5.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>9</v>
@@ -4415,7 +4482,7 @@
         <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22" t="n">
         <v>27</v>
@@ -4436,10 +4503,10 @@
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" t="n">
         <v>40</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4513,19 +4580,19 @@
         <v>11.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.314</v>
+        <v>0.315</v>
       </c>
       <c r="O23" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P23" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q23" t="n">
         <v>0.707</v>
       </c>
       <c r="R23" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S23" t="n">
         <v>29</v>
@@ -4534,7 +4601,7 @@
         <v>41.9</v>
       </c>
       <c r="U23" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
         <v>14.4</v>
@@ -4543,34 +4610,34 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA23" t="n">
         <v>20.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
         <v>0.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
@@ -4621,10 +4688,10 @@
         <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
@@ -4633,7 +4700,7 @@
         <v>18</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -4665,19 +4732,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F24" t="n">
         <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>0.667</v>
+        <v>0.663</v>
       </c>
       <c r="H24" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I24" t="n">
         <v>41.4</v>
@@ -4695,31 +4762,31 @@
         <v>21.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="O24" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P24" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="R24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
         <v>32.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U24" t="n">
         <v>26.7</v>
       </c>
       <c r="V24" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W24" t="n">
         <v>6.5</v>
@@ -4734,28 +4801,28 @@
         <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.2</v>
+        <v>110.1</v>
       </c>
       <c r="AC24" t="n">
         <v>5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4776,10 +4843,10 @@
         <v>1</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ24" t="n">
         <v>5</v>
@@ -4791,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4812,7 +4879,7 @@
         <v>9</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -4925,28 +4992,28 @@
         <v>-1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4955,13 +5022,13 @@
         <v>18</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>24</v>
       </c>
       <c r="AP25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ25" t="n">
         <v>10</v>
@@ -4994,7 +5061,7 @@
         <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" t="n">
         <v>38</v>
       </c>
       <c r="F26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G26" t="n">
-        <v>0.469</v>
+        <v>0.475</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,19 +5114,19 @@
         <v>37.1</v>
       </c>
       <c r="J26" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K26" t="n">
         <v>0.464</v>
       </c>
       <c r="L26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O26" t="n">
         <v>22.2</v>
@@ -5074,10 +5141,10 @@
         <v>10.1</v>
       </c>
       <c r="S26" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="T26" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="U26" t="n">
         <v>19.1</v>
@@ -5095,7 +5162,7 @@
         <v>5.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA26" t="n">
         <v>23.1</v>
@@ -5107,7 +5174,7 @@
         <v>-2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5137,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5152,22 +5219,22 @@
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
       </c>
       <c r="AV26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW26" t="n">
         <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -5211,31 +5278,31 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F27" t="n">
         <v>26</v>
       </c>
       <c r="G27" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
       </c>
       <c r="I27" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J27" t="n">
         <v>78.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L27" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M27" t="n">
         <v>19.7</v>
@@ -5256,10 +5323,10 @@
         <v>9.5</v>
       </c>
       <c r="S27" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T27" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U27" t="n">
         <v>20.9</v>
@@ -5280,19 +5347,19 @@
         <v>18.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF27" t="n">
         <v>5</v>
@@ -5301,7 +5368,7 @@
         <v>5</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>26</v>
@@ -5310,19 +5377,19 @@
         <v>27</v>
       </c>
       <c r="AK27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL27" t="n">
         <v>9</v>
       </c>
       <c r="AM27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN27" t="n">
         <v>11</v>
       </c>
       <c r="AO27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP27" t="n">
         <v>27</v>
@@ -5334,10 +5401,10 @@
         <v>27</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AU27" t="n">
         <v>21</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5550,7 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5492,7 +5559,7 @@
         <v>3</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5540,13 +5607,13 @@
         <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" t="n">
         <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>0.506</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,7 +5660,7 @@
         <v>38.4</v>
       </c>
       <c r="J29" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
         <v>0.469</v>
@@ -5626,7 +5693,7 @@
         <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V29" t="n">
         <v>11.7</v>
@@ -5635,25 +5702,25 @@
         <v>6.9</v>
       </c>
       <c r="X29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
         <v>4</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>15</v>
@@ -5677,7 +5744,7 @@
         <v>7</v>
       </c>
       <c r="AL29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5701,7 +5768,7 @@
         <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU29" t="n">
         <v>5</v>
@@ -5710,10 +5777,10 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY29" t="n">
         <v>4</v>
@@ -5725,7 +5792,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F30" t="n">
         <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.667</v>
+        <v>0.663</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5784,16 +5851,16 @@
         <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O30" t="n">
         <v>21.3</v>
       </c>
       <c r="P30" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="n">
         <v>0.759</v>
@@ -5805,13 +5872,13 @@
         <v>29.4</v>
       </c>
       <c r="T30" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="V30" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
         <v>8.800000000000001</v>
@@ -5820,34 +5887,34 @@
         <v>4.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="AA30" t="n">
         <v>23.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.5</v>
+        <v>106.6</v>
       </c>
       <c r="AC30" t="n">
         <v>7.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
         <v>4</v>
@@ -5865,13 +5932,13 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ30" t="n">
         <v>16</v>
@@ -5898,7 +5965,7 @@
         <v>22</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>30</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" t="n">
         <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>0.531</v>
+        <v>0.525</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>0.446</v>
@@ -5969,25 +6036,25 @@
         <v>19.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O31" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P31" t="n">
         <v>24.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R31" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S31" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="U31" t="n">
         <v>19.6</v>
@@ -5999,7 +6066,7 @@
         <v>7.8</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y31" t="n">
         <v>4.4</v>
@@ -6011,13 +6078,13 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6029,25 +6096,25 @@
         <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>22</v>
       </c>
       <c r="AL31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6059,13 +6126,13 @@
         <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
         <v>27</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6074,10 +6141,10 @@
         <v>7</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6086,7 +6153,7 @@
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-14-2007-08</t>
+          <t>2008-04-14</t>
         </is>
       </c>
     </row>
